--- a/VerveStacks_COL/SuppXLS/Scen_Base_VS.xlsx
+++ b/VerveStacks_COL/SuppXLS/Scen_Base_VS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_COL\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{067E3EF6-6DA2-41F8-B620-FCEFF0AB1BF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9440315F-4179-439B-A07A-AD3D4CC9D8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1690,7 +1690,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45D96609-B25B-4606-9CDE-649F38E09E05}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{732426DD-C62F-4497-9134-E6CE1660C89A}">
   <dimension ref="B9:L16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
